--- a/data/exports/黄老师/dist_order_2026-10-16.xlsx
+++ b/data/exports/黄老师/dist_order_2026-10-16.xlsx
@@ -30334,7 +30334,7 @@
       </c>
       <c r="B505" s="0" t="inlineStr">
         <is>
-          <t>冬日暖阳🌻</t>
+          <t>暖阳阳🌻</t>
         </is>
       </c>
       <c r="C505" s="0" t="inlineStr">
